--- a/01_Raw_data/Depth_length_velocity_width/length width.xlsx
+++ b/01_Raw_data/Depth_length_velocity_width/length width.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\SpringsProject_Sam&amp;Paul\Depth_length_velocity_width\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SpringMetabolism_FlowReversals\01_Raw_data\Depth_length_velocity_width\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F55817-E715-4A8C-A754-8DBB657120D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BBE67C-1A14-49AC-BBC6-13307F62DF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" activeTab="1" xr2:uid="{40B71AB7-011B-4E1A-BEB0-517F5763788F}"/>
+    <workbookView xWindow="-28920" yWindow="-2640" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{40B71AB7-011B-4E1A-BEB0-517F5763788F}"/>
   </bookViews>
   <sheets>
     <sheet name="length " sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t xml:space="preserve">Otter </t>
   </si>
@@ -62,7 +62,22 @@
     <t>m</t>
   </si>
   <si>
-    <t>17..5</t>
+    <t>w</t>
+  </si>
+  <si>
+    <t>OS</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>LG</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>AM</t>
   </si>
 </sst>
 </file>
@@ -125,9 +140,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -165,7 +180,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -271,7 +286,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -413,7 +428,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -510,47 +525,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>16.86</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
-        <f>CONVERT(69.6, "ft","m")</f>
-        <v>21.214079999999996</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1">
-        <f>CONVERT(23.4, "ft","m")</f>
-        <v>7.13232</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1">
-        <f>CONVERT(7.4, "ft","m")</f>
-        <v>2.2555200000000002</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/01_Raw_data/Depth_length_velocity_width/length width.xlsx
+++ b/01_Raw_data/Depth_length_velocity_width/length width.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SpringMetabolism_FlowReversals\01_Raw_data\Depth_length_velocity_width\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BBE67C-1A14-49AC-BBC6-13307F62DF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73274876-C2B5-4F0D-A758-DD7B492CBA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-2640" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{40B71AB7-011B-4E1A-BEB0-517F5763788F}"/>
   </bookViews>
@@ -71,13 +71,13 @@
     <t>GB</t>
   </si>
   <si>
-    <t>LG</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
     <t>AM</t>
+  </si>
+  <si>
+    <t>LF</t>
   </si>
 </sst>
 </file>
@@ -525,7 +525,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
         <v>8</v>
@@ -549,7 +549,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
         <v>20</v>
@@ -557,7 +557,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>50</v>
@@ -565,7 +565,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1">
         <v>30</v>

--- a/01_Raw_data/Depth_length_velocity_width/length width.xlsx
+++ b/01_Raw_data/Depth_length_velocity_width/length width.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SpringMetabolism_FlowReversals\01_Raw_data\Depth_length_velocity_width\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73274876-C2B5-4F0D-A758-DD7B492CBA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A32590-E278-42C7-8D15-50A46D165C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2640" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{40B71AB7-011B-4E1A-BEB0-517F5763788F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{40B71AB7-011B-4E1A-BEB0-517F5763788F}"/>
   </bookViews>
   <sheets>
     <sheet name="length " sheetId="1" r:id="rId1"/>
-    <sheet name="width " sheetId="2" r:id="rId2"/>
+    <sheet name="depth threshold" sheetId="3" r:id="rId2"/>
+    <sheet name="width " sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,29 +37,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
-  <si>
-    <t xml:space="preserve">Otter </t>
-  </si>
-  <si>
-    <t>site</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="9">
   <si>
     <t>km</t>
   </si>
   <si>
-    <t xml:space="preserve">Gilchrist Blue </t>
-  </si>
-  <si>
-    <t>Little Fanning</t>
-  </si>
-  <si>
-    <t>Ichetucknee</t>
-  </si>
-  <si>
-    <t>Allen Mill</t>
-  </si>
-  <si>
     <t>m</t>
   </si>
   <si>
@@ -78,6 +61,9 @@
   </si>
   <si>
     <t>LF</t>
+  </si>
+  <si>
+    <t>max</t>
   </si>
 </sst>
 </file>
@@ -441,18 +427,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>1.35</v>
@@ -464,7 +450,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0.35</v>
@@ -476,7 +462,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>0.32</v>
@@ -516,6 +502,64 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{158E618A-3DE4-41A4-BE7B-7DB5C9D41201}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>1.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{220BE196-BC35-49F2-97CC-84B00D974150}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -525,15 +569,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>16.86</v>
@@ -541,7 +585,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1">
         <v>16.5</v>
@@ -549,7 +593,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1">
         <v>20</v>
@@ -557,7 +601,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>50</v>
@@ -565,7 +609,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1">
         <v>30</v>

--- a/01_Raw_data/Depth_length_velocity_width/length width.xlsx
+++ b/01_Raw_data/Depth_length_velocity_width/length width.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SpringMetabolism_FlowReversals\01_Raw_data\Depth_length_velocity_width\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A32590-E278-42C7-8D15-50A46D165C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B490192-E757-45F0-9B51-6C19F1714EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{40B71AB7-011B-4E1A-BEB0-517F5763788F}"/>
+    <workbookView xWindow="17910" yWindow="-1860" windowWidth="19380" windowHeight="10260" xr2:uid="{40B71AB7-011B-4E1A-BEB0-517F5763788F}"/>
   </bookViews>
   <sheets>
     <sheet name="length " sheetId="1" r:id="rId1"/>
@@ -477,11 +477,11 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>7.96</v>
+        <v>2.5</v>
       </c>
       <c r="C5">
         <f t="shared" si="0"/>
-        <v>7960</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">

--- a/01_Raw_data/Depth_length_velocity_width/length width.xlsx
+++ b/01_Raw_data/Depth_length_velocity_width/length width.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SpringMetabolism_FlowReversals\01_Raw_data\Depth_length_velocity_width\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B490192-E757-45F0-9B51-6C19F1714EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB28AB1-7609-49EC-8EF9-36F94093B0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17910" yWindow="-1860" windowWidth="19380" windowHeight="10260" xr2:uid="{40B71AB7-011B-4E1A-BEB0-517F5763788F}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{40B71AB7-011B-4E1A-BEB0-517F5763788F}"/>
   </bookViews>
   <sheets>
     <sheet name="length " sheetId="1" r:id="rId1"/>
@@ -423,9 +423,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1483E31B-06A5-4149-B6E5-C27153C75F7E}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -436,7 +436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -448,7 +448,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -456,11 +456,11 @@
         <v>0.35</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C6" si="0">B3*1000</f>
+        <f t="shared" ref="C3:C5" si="0">B3*1000</f>
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -472,7 +472,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -484,7 +484,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -492,8 +492,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
@@ -504,9 +503,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{158E618A-3DE4-41A4-BE7B-7DB5C9D41201}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -514,7 +513,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -522,7 +521,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -530,7 +529,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -538,7 +537,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -546,7 +545,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -562,12 +561,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{220BE196-BC35-49F2-97CC-84B00D974150}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -575,7 +574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -583,7 +582,7 @@
         <v>16.86</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -591,7 +590,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -599,7 +598,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -607,12 +606,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>30</v>
+        <v>16.5</v>
       </c>
     </row>
   </sheetData>
